--- a/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0236</v>
+        <v>0.03165</v>
       </c>
       <c r="E2">
-        <v>-0.0849</v>
+        <v>-0.001699999999999998</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,103 +600,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.002023394517692105</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.00165391002817897</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>824.1</v>
+        <v>866.3000000000001</v>
       </c>
       <c r="L2">
-        <v>0.3458826492067489</v>
+        <v>0.3695030923437834</v>
       </c>
       <c r="M2">
-        <v>450.3</v>
+        <v>800</v>
       </c>
       <c r="N2">
-        <v>0.0499024779467175</v>
+        <v>0.07482929566925452</v>
       </c>
       <c r="O2">
-        <v>0.5464142701128504</v>
+        <v>0.9234676209165416</v>
       </c>
       <c r="P2">
-        <v>450.3</v>
+        <v>540.3000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.0499024779467175</v>
+        <v>0.05053783556262277</v>
       </c>
       <c r="R2">
-        <v>0.5464142701128504</v>
+        <v>0.6236869444765093</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>259.7</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.324625</v>
       </c>
       <c r="U2">
-        <v>9012.299999999999</v>
+        <v>3526.6</v>
       </c>
       <c r="V2">
-        <v>0.9987477281794405</v>
+        <v>0.3298662426339912</v>
       </c>
       <c r="W2">
-        <v>0.04665944384254243</v>
+        <v>0.06461626927257887</v>
       </c>
       <c r="X2">
-        <v>0.1118560292820187</v>
+        <v>0.1299329639782141</v>
       </c>
       <c r="Y2">
-        <v>-0.06519658543947629</v>
+        <v>-0.06531669470563524</v>
       </c>
       <c r="Z2">
-        <v>0.2616089004154331</v>
+        <v>0.1535262916639382</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.074810229620805</v>
+        <v>0.1080162499044234</v>
       </c>
       <c r="AC2">
-        <v>-0.074810229620805</v>
+        <v>-0.1080162499044234</v>
       </c>
       <c r="AD2">
-        <v>9619.6</v>
+        <v>8918</v>
       </c>
       <c r="AE2">
-        <v>5.645301110733953</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>9625.245301110734</v>
+        <v>8918</v>
       </c>
       <c r="AG2">
-        <v>612.9453011107344</v>
+        <v>5391.4</v>
       </c>
       <c r="AH2">
-        <v>0.5161308995649961</v>
+        <v>0.4547911673211281</v>
       </c>
       <c r="AI2">
-        <v>0.4131051724694983</v>
+        <v>0.4038784650987958</v>
       </c>
       <c r="AJ2">
-        <v>0.06360633214063598</v>
+        <v>0.335236034422723</v>
       </c>
       <c r="AK2">
-        <v>0.04290097272065026</v>
+        <v>0.2905741526223032</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>1616.739495798319</v>
-      </c>
-      <c r="AP2">
-        <v>103.0160169934007</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0741</v>
+        <v>0.0352</v>
       </c>
       <c r="E3">
-        <v>-0.113</v>
+        <v>-0.266</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>30.6</v>
+        <v>16.6</v>
       </c>
       <c r="L3">
-        <v>0.1262897234832852</v>
+        <v>0.07457322551662175</v>
       </c>
       <c r="M3">
-        <v>52.9</v>
+        <v>30.9</v>
       </c>
       <c r="N3">
-        <v>0.07607132585562267</v>
+        <v>0.05189788377561303</v>
       </c>
       <c r="O3">
-        <v>1.72875816993464</v>
+        <v>1.86144578313253</v>
       </c>
       <c r="P3">
-        <v>52.9</v>
+        <v>30.9</v>
       </c>
       <c r="Q3">
-        <v>0.07607132585562267</v>
+        <v>0.05189788377561303</v>
       </c>
       <c r="R3">
-        <v>1.72875816993464</v>
+        <v>1.86144578313253</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>594.6</v>
+        <v>464.6</v>
       </c>
       <c r="V3">
-        <v>0.8550474547023297</v>
+        <v>0.7803157541148809</v>
       </c>
       <c r="W3">
-        <v>0.02719758243711671</v>
+        <v>0.01191330558346491</v>
       </c>
       <c r="X3">
-        <v>0.07184010103233614</v>
+        <v>0.104209480681358</v>
       </c>
       <c r="Y3">
-        <v>-0.04464251859521944</v>
+        <v>-0.0922961750978931</v>
       </c>
       <c r="Z3">
-        <v>0.5389234875444839</v>
+        <v>0.2219784603111288</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06558115753388757</v>
+        <v>0.1007841273168596</v>
       </c>
       <c r="AC3">
-        <v>-0.06558115753388757</v>
+        <v>-0.1007841273168596</v>
       </c>
       <c r="AD3">
-        <v>220.9</v>
+        <v>152.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>220.9</v>
+        <v>152.2</v>
       </c>
       <c r="AG3">
-        <v>-373.7</v>
+        <v>-312.4</v>
       </c>
       <c r="AH3">
-        <v>0.2410782494816109</v>
+        <v>0.2035848047084002</v>
       </c>
       <c r="AI3">
-        <v>0.1368394969956018</v>
+        <v>0.1058488072884067</v>
       </c>
       <c r="AJ3">
-        <v>-1.161641280696301</v>
+        <v>-1.103886925795053</v>
       </c>
       <c r="AK3">
-        <v>-0.3664803373541238</v>
+        <v>-0.320969896229323</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HSBC Bank Oman S.A.O.G. (MSM:HBMO)</t>
+          <t>Ahli Bank SAOG (MSM:ABOB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00724</v>
+        <v>0.0823</v>
       </c>
       <c r="E4">
-        <v>-0.215</v>
+        <v>0.0223</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,82 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>14.2</v>
+        <v>82</v>
       </c>
       <c r="L4">
-        <v>0.07442348008385744</v>
+        <v>0.4087736789631107</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>62.1</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.07170900692840647</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.7573170731707317</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>62.1</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.07170900692840647</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.7573170731707317</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>2073.4</v>
+        <v>327.8</v>
       </c>
       <c r="V4">
-        <v>3.828286558345642</v>
+        <v>0.3785219399538106</v>
       </c>
       <c r="W4">
-        <v>0.0162341374185435</v>
+        <v>0.07427536231884058</v>
       </c>
       <c r="X4">
-        <v>0.07235587727299309</v>
+        <v>0.1196957586560247</v>
       </c>
       <c r="Y4">
-        <v>-0.05612173985444958</v>
+        <v>-0.04542039633718416</v>
       </c>
       <c r="Z4">
-        <v>-0.1544064093226512</v>
+        <v>0.0932806324110672</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06576757611115544</v>
+        <v>0.1076462243493068</v>
       </c>
       <c r="AC4">
-        <v>-0.06576757611115544</v>
+        <v>-0.1076462243493068</v>
       </c>
       <c r="AD4">
-        <v>179.4</v>
+        <v>515</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>179.4</v>
+        <v>515</v>
       </c>
       <c r="AG4">
-        <v>-1894</v>
+        <v>187.2</v>
       </c>
       <c r="AH4">
-        <v>0.2488210818307906</v>
+        <v>0.3729181752353367</v>
       </c>
       <c r="AI4">
-        <v>0.1680876979293545</v>
+        <v>0.3042296786389414</v>
       </c>
       <c r="AJ4">
-        <v>1.400473232771369</v>
+        <v>0.1777440182301557</v>
       </c>
       <c r="AK4">
-        <v>1.882516648444489</v>
+        <v>0.1371428571428571</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank Dhofar SAOG (MSM:BKDB)</t>
+          <t>National Bank of Oman SAOG (MSM:NBOB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0233</v>
+        <v>-0.0144</v>
       </c>
       <c r="E5">
-        <v>-0.0849</v>
+        <v>-0.0257</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,34 +966,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.01846395931770666</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.01585594868736529</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>83.90000000000001</v>
+        <v>109.9</v>
       </c>
       <c r="L5">
-        <v>0.3213328226733053</v>
+        <v>0.3801452784503632</v>
       </c>
       <c r="M5">
-        <v>55.6</v>
+        <v>39.6</v>
       </c>
       <c r="N5">
-        <v>0.05701979284175982</v>
+        <v>0.032368808239333</v>
       </c>
       <c r="O5">
-        <v>0.6626936829558998</v>
+        <v>0.3603275705186533</v>
       </c>
       <c r="P5">
-        <v>55.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q5">
-        <v>0.05701979284175982</v>
+        <v>0.032368808239333</v>
       </c>
       <c r="R5">
-        <v>0.6626936829558998</v>
+        <v>0.3603275705186533</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,67 +1002,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>500</v>
+        <v>546.8</v>
       </c>
       <c r="V5">
-        <v>0.5127679212388473</v>
+        <v>0.4469511198299819</v>
       </c>
       <c r="W5">
-        <v>0.04638947252018136</v>
+        <v>0.07644685587089595</v>
       </c>
       <c r="X5">
-        <v>0.1118560292820187</v>
+        <v>0.1368228585110135</v>
       </c>
       <c r="Y5">
-        <v>-0.06546655676183735</v>
+        <v>-0.06037600264011758</v>
       </c>
       <c r="Z5">
-        <v>0.08765014784295337</v>
+        <v>0.1280109812256465</v>
       </c>
       <c r="AA5">
-        <v>0.00138977624663785</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07370036858073459</v>
+        <v>0.1076719029888328</v>
       </c>
       <c r="AC5">
-        <v>-0.07231059233409674</v>
+        <v>-0.1076719029888328</v>
       </c>
       <c r="AD5">
-        <v>1331.6</v>
+        <v>1186.3</v>
       </c>
       <c r="AE5">
-        <v>5.645301110733953</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1337.245301110734</v>
+        <v>1186.3</v>
       </c>
       <c r="AG5">
-        <v>837.2453011107339</v>
+        <v>639.5</v>
       </c>
       <c r="AH5">
-        <v>0.5783069252106892</v>
+        <v>0.4923019463003694</v>
       </c>
       <c r="AI5">
-        <v>0.4210940373734467</v>
+        <v>0.4404633720714365</v>
       </c>
       <c r="AJ5">
-        <v>0.4619678714633522</v>
+        <v>0.3432819797090558</v>
       </c>
       <c r="AK5">
-        <v>0.3129134122385991</v>
+        <v>0.2979268576752854</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>223.7983193277311</v>
-      </c>
-      <c r="AP5">
-        <v>140.7134959849973</v>
       </c>
     </row>
     <row r="6">
@@ -1076,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Bank of Oman SAOG (MSM:NBOB)</t>
+          <t>Bank Dhofar SAOG (MSM:BKDB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0669</v>
+        <v>-0.019</v>
       </c>
       <c r="E6">
-        <v>-0.16</v>
+        <v>-0.128</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>64.59999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="L6">
-        <v>0.2706325932132383</v>
+        <v>0.2276205049732211</v>
       </c>
       <c r="M6">
-        <v>22.5</v>
+        <v>39.9</v>
       </c>
       <c r="N6">
-        <v>0.02717391304347826</v>
+        <v>0.02922648696161734</v>
       </c>
       <c r="O6">
-        <v>0.348297213622291</v>
+        <v>0.6705882352941176</v>
       </c>
       <c r="P6">
-        <v>22.5</v>
+        <v>39.9</v>
       </c>
       <c r="Q6">
-        <v>0.02717391304347826</v>
+        <v>0.02922648696161734</v>
       </c>
       <c r="R6">
-        <v>0.348297213622291</v>
+        <v>0.6705882352941176</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1133,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>555.7</v>
+        <v>452.9</v>
       </c>
       <c r="V6">
-        <v>0.6711352657004831</v>
+        <v>0.3317462642836214</v>
       </c>
       <c r="W6">
-        <v>0.04665944384254243</v>
+        <v>0.0323651000870322</v>
       </c>
       <c r="X6">
-        <v>0.1229086288988374</v>
+        <v>0.1409747329215973</v>
       </c>
       <c r="Y6">
-        <v>-0.07624918505629499</v>
+        <v>-0.1086096328345651</v>
       </c>
       <c r="Z6">
-        <v>0.1332626172398392</v>
+        <v>0.09790262172284643</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.074810229620805</v>
+        <v>0.1083605968200139</v>
       </c>
       <c r="AC6">
-        <v>-0.074810229620805</v>
+        <v>-0.1083605968200139</v>
       </c>
       <c r="AD6">
-        <v>1376.5</v>
+        <v>1447.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1376.5</v>
+        <v>1447.9</v>
       </c>
       <c r="AG6">
-        <v>820.8</v>
+        <v>995.0000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.6244046268995237</v>
+        <v>0.5146990864171199</v>
       </c>
       <c r="AI6">
-        <v>0.4891439536619168</v>
+        <v>0.4402919264102175</v>
       </c>
       <c r="AJ6">
-        <v>0.4978165938864629</v>
+        <v>0.4215744428438268</v>
       </c>
       <c r="AK6">
-        <v>0.3634431455897981</v>
+        <v>0.3508957539850473</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0236</v>
+        <v>0.0281</v>
       </c>
       <c r="E7">
-        <v>0.0156</v>
+        <v>0.0308</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1225,28 +1216,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>495.5</v>
+        <v>513.6</v>
       </c>
       <c r="L7">
-        <v>0.4584991209401314</v>
+        <v>0.4545937334041424</v>
       </c>
       <c r="M7">
-        <v>230.1</v>
+        <v>297.1</v>
       </c>
       <c r="N7">
-        <v>0.05119248909851384</v>
+        <v>0.05528161807119067</v>
       </c>
       <c r="O7">
-        <v>0.4643794147325933</v>
+        <v>0.5784657320872274</v>
       </c>
       <c r="P7">
-        <v>230.1</v>
+        <v>297.1</v>
       </c>
       <c r="Q7">
-        <v>0.05119248909851384</v>
+        <v>0.05528161807119067</v>
       </c>
       <c r="R7">
-        <v>0.4643794147325933</v>
+        <v>0.5784657320872274</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1255,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>4804</v>
+        <v>1518.3</v>
       </c>
       <c r="V7">
-        <v>1.06879060247397</v>
+        <v>0.2825112107623318</v>
       </c>
       <c r="W7">
-        <v>0.09560653713315453</v>
+        <v>0.09385964912280702</v>
       </c>
       <c r="X7">
-        <v>0.07982235053230187</v>
+        <v>0.1230430694454147</v>
       </c>
       <c r="Y7">
-        <v>0.01578418660085266</v>
+        <v>-0.02918342032260765</v>
       </c>
       <c r="Z7">
-        <v>0.4668048896375968</v>
+        <v>0.3715714003815036</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07491574918819659</v>
+        <v>0.1126092921475042</v>
       </c>
       <c r="AC7">
-        <v>-0.07491574918819659</v>
+        <v>-0.1126092921475042</v>
       </c>
       <c r="AD7">
-        <v>2372.6</v>
+        <v>3589.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2372.6</v>
+        <v>3589.9</v>
       </c>
       <c r="AG7">
-        <v>-2431.4</v>
+        <v>2071.6</v>
       </c>
       <c r="AH7">
-        <v>0.3454873751346944</v>
+        <v>0.4004707614734165</v>
       </c>
       <c r="AI7">
-        <v>0.3024500930576447</v>
+        <v>0.388862410364176</v>
       </c>
       <c r="AJ7">
-        <v>-1.178346418532519</v>
+        <v>0.2782202285821728</v>
       </c>
       <c r="AK7">
-        <v>-0.7996448069459976</v>
+        <v>0.2685680948985545</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.07440000000000001</v>
+        <v>0.0771</v>
       </c>
       <c r="E8">
-        <v>0.0608</v>
+        <v>0.0535</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,212 +1338,90 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>67.8</v>
+        <v>84.7</v>
       </c>
       <c r="L8">
-        <v>0.327852998065764</v>
+        <v>0.3514522821576764</v>
       </c>
       <c r="M8">
-        <v>39.7</v>
+        <v>330.4</v>
       </c>
       <c r="N8">
-        <v>0.0440572633448008</v>
+        <v>0.2608352411778637</v>
       </c>
       <c r="O8">
-        <v>0.5855457227138644</v>
+        <v>3.900826446280991</v>
       </c>
       <c r="P8">
-        <v>39.7</v>
+        <v>70.7</v>
       </c>
       <c r="Q8">
-        <v>0.0440572633448008</v>
+        <v>0.05581432067577169</v>
       </c>
       <c r="R8">
-        <v>0.5855457227138644</v>
+        <v>0.8347107438016529</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>259.7</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.7860169491525424</v>
       </c>
       <c r="U8">
-        <v>207.2</v>
+        <v>216.2</v>
       </c>
       <c r="V8">
-        <v>0.2299411829985573</v>
+        <v>0.1706797189547643</v>
       </c>
       <c r="W8">
-        <v>0.04932702801018552</v>
+        <v>0.05495717622631716</v>
       </c>
       <c r="X8">
-        <v>0.1783977295904248</v>
+        <v>0.1656115631938485</v>
       </c>
       <c r="Y8">
-        <v>-0.1290707015802393</v>
+        <v>-0.1106543869675314</v>
       </c>
       <c r="Z8">
-        <v>0.1609463771499728</v>
+        <v>0.05809048617639261</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07801455083633975</v>
+        <v>0.1174718848592197</v>
       </c>
       <c r="AC8">
-        <v>-0.07801455083633975</v>
+        <v>-0.1174718848592197</v>
       </c>
       <c r="AD8">
-        <v>2814.7</v>
+        <v>2026.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2814.7</v>
+        <v>2026.7</v>
       </c>
       <c r="AG8">
-        <v>2607.5</v>
+        <v>1810.5</v>
       </c>
       <c r="AH8">
-        <v>0.757495021260563</v>
+        <v>0.6153822797109371</v>
       </c>
       <c r="AI8">
-        <v>0.6461810418053674</v>
+        <v>0.5423914788845474</v>
       </c>
       <c r="AJ8">
-        <v>0.7431739155218606</v>
+        <v>0.5883595476407124</v>
       </c>
       <c r="AK8">
-        <v>0.6285101357051607</v>
+        <v>0.5142881490739688</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ahli Bank SAOG (MSM:ABOB)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.0458</v>
-      </c>
-      <c r="E9">
-        <v>-0.008159999999999999</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>67.5</v>
-      </c>
-      <c r="L9">
-        <v>0.4161528976572134</v>
-      </c>
-      <c r="M9">
-        <v>49.5</v>
-      </c>
-      <c r="N9">
-        <v>0.08424098025867938</v>
-      </c>
-      <c r="O9">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="P9">
-        <v>49.5</v>
-      </c>
-      <c r="Q9">
-        <v>0.08424098025867938</v>
-      </c>
-      <c r="R9">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>277.4</v>
-      </c>
-      <c r="V9">
-        <v>0.4720898570456092</v>
-      </c>
-      <c r="W9">
-        <v>0.06771669341894061</v>
-      </c>
-      <c r="X9">
-        <v>0.1453377746664797</v>
-      </c>
-      <c r="Y9">
-        <v>-0.07762108124753909</v>
-      </c>
-      <c r="Z9">
-        <v>0.1064653757794552</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.08096423639426635</v>
-      </c>
-      <c r="AC9">
-        <v>-0.08096423639426635</v>
-      </c>
-      <c r="AD9">
-        <v>1323.9</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>1323.9</v>
-      </c>
-      <c r="AG9">
-        <v>1046.5</v>
-      </c>
-      <c r="AH9">
-        <v>0.6925974365681402</v>
-      </c>
-      <c r="AI9">
-        <v>0.5452860496725566</v>
-      </c>
-      <c r="AJ9">
-        <v>0.6404136833731107</v>
-      </c>
-      <c r="AK9">
-        <v>0.4866310160427808</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03165</v>
+        <v>0.03545</v>
       </c>
       <c r="E2">
-        <v>-0.001699999999999998</v>
+        <v>0.0322</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>866.3000000000001</v>
+        <v>1090</v>
       </c>
       <c r="L2">
-        <v>0.3695030923437834</v>
+        <v>0.4200061652281135</v>
       </c>
       <c r="M2">
-        <v>800</v>
+        <v>615.6</v>
       </c>
       <c r="N2">
-        <v>0.07482929566925452</v>
+        <v>0.05780173142288408</v>
       </c>
       <c r="O2">
-        <v>0.9234676209165416</v>
+        <v>0.5647706422018349</v>
       </c>
       <c r="P2">
-        <v>540.3000000000001</v>
+        <v>615.6</v>
       </c>
       <c r="Q2">
-        <v>0.05053783556262277</v>
+        <v>0.05780173142288408</v>
       </c>
       <c r="R2">
-        <v>0.6236869444765093</v>
+        <v>0.5647706422018349</v>
       </c>
       <c r="S2">
-        <v>259.7</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.324625</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>3526.6</v>
+        <v>5033</v>
       </c>
       <c r="V2">
-        <v>0.3298662426339912</v>
+        <v>0.4725732850087322</v>
       </c>
       <c r="W2">
-        <v>0.06461626927257887</v>
+        <v>0.08099214823911943</v>
       </c>
       <c r="X2">
-        <v>0.1299329639782141</v>
+        <v>0.09358289668954142</v>
       </c>
       <c r="Y2">
-        <v>-0.06531669470563524</v>
+        <v>-0.01259074845042199</v>
       </c>
       <c r="Z2">
-        <v>0.1535262916639382</v>
+        <v>0.1455973519593817</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1080162499044234</v>
+        <v>0.08142435415946919</v>
       </c>
       <c r="AC2">
-        <v>-0.1080162499044234</v>
+        <v>-0.08142435415946919</v>
       </c>
       <c r="AD2">
-        <v>8918</v>
+        <v>8917.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8918</v>
+        <v>8917.1</v>
       </c>
       <c r="AG2">
-        <v>5391.4</v>
+        <v>3884.1</v>
       </c>
       <c r="AH2">
-        <v>0.4547911673211281</v>
+        <v>0.4557143806248179</v>
       </c>
       <c r="AI2">
-        <v>0.4038784650987958</v>
+        <v>0.3836384365521544</v>
       </c>
       <c r="AJ2">
-        <v>0.335236034422723</v>
+        <v>0.2672368122303792</v>
       </c>
       <c r="AK2">
-        <v>0.2905741526223032</v>
+        <v>0.2132890365448505</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oman Arab Bank SAOG (MSM:OAB)</t>
+          <t>Ahli Bank SAOG (MSM:ABOB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0352</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.266</v>
+        <v>0.0549</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>16.6</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="L3">
-        <v>0.07457322551662175</v>
+        <v>0.4438845625286303</v>
       </c>
       <c r="M3">
-        <v>30.9</v>
+        <v>79.2</v>
       </c>
       <c r="N3">
-        <v>0.05189788377561303</v>
+        <v>0.08110599078341015</v>
       </c>
       <c r="O3">
-        <v>1.86144578313253</v>
+        <v>0.8173374613003096</v>
       </c>
       <c r="P3">
-        <v>30.9</v>
+        <v>79.2</v>
       </c>
       <c r="Q3">
-        <v>0.05189788377561303</v>
+        <v>0.08110599078341015</v>
       </c>
       <c r="R3">
-        <v>1.86144578313253</v>
+        <v>0.8173374613003096</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>464.6</v>
+        <v>226.8</v>
       </c>
       <c r="V3">
-        <v>0.7803157541148809</v>
+        <v>0.232258064516129</v>
       </c>
       <c r="W3">
-        <v>0.01191330558346491</v>
+        <v>0.08227203260315843</v>
       </c>
       <c r="X3">
-        <v>0.104209480681358</v>
+        <v>0.08389362585645024</v>
       </c>
       <c r="Y3">
-        <v>-0.0922961750978931</v>
+        <v>-0.001621593253291809</v>
       </c>
       <c r="Z3">
-        <v>0.2219784603111288</v>
+        <v>0.1599267399267399</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1007841273168596</v>
+        <v>0.07913623110316884</v>
       </c>
       <c r="AC3">
-        <v>-0.1007841273168596</v>
+        <v>-0.07913623110316884</v>
       </c>
       <c r="AD3">
-        <v>152.2</v>
+        <v>444.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>152.2</v>
+        <v>444.2</v>
       </c>
       <c r="AG3">
-        <v>-312.4</v>
+        <v>217.4</v>
       </c>
       <c r="AH3">
-        <v>0.2035848047084002</v>
+        <v>0.3126627718730203</v>
       </c>
       <c r="AI3">
-        <v>0.1058488072884067</v>
+        <v>0.2487400604770971</v>
       </c>
       <c r="AJ3">
-        <v>-1.103886925795053</v>
+        <v>0.182092302537901</v>
       </c>
       <c r="AK3">
-        <v>-0.320969896229323</v>
+        <v>0.1394483643361129</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ahli Bank SAOG (MSM:ABOB)</t>
+          <t>National Bank of Oman SAOG (MSM:NBOB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0823</v>
+        <v>0.0175</v>
       </c>
       <c r="E4">
-        <v>0.0223</v>
+        <v>0.0333</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>82</v>
+        <v>145.5</v>
       </c>
       <c r="L4">
-        <v>0.4087736789631107</v>
+        <v>0.4311111111111111</v>
       </c>
       <c r="M4">
-        <v>62.1</v>
+        <v>59.8</v>
       </c>
       <c r="N4">
-        <v>0.07170900692840647</v>
+        <v>0.0488282844778313</v>
       </c>
       <c r="O4">
-        <v>0.7573170731707317</v>
+        <v>0.4109965635738831</v>
       </c>
       <c r="P4">
-        <v>62.1</v>
+        <v>59.8</v>
       </c>
       <c r="Q4">
-        <v>0.07170900692840647</v>
+        <v>0.0488282844778313</v>
       </c>
       <c r="R4">
-        <v>0.7573170731707317</v>
+        <v>0.4109965635738831</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>327.8</v>
+        <v>719.1</v>
       </c>
       <c r="V4">
-        <v>0.3785219399538106</v>
+        <v>0.5871642034784029</v>
       </c>
       <c r="W4">
-        <v>0.07427536231884058</v>
+        <v>0.09654943596549435</v>
       </c>
       <c r="X4">
-        <v>0.1196957586560247</v>
+        <v>0.09675630249396888</v>
       </c>
       <c r="Y4">
-        <v>-0.04542039633718416</v>
+        <v>-0.000206866528474528</v>
       </c>
       <c r="Z4">
-        <v>0.0932806324110672</v>
+        <v>0.1572327044025157</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1076462243493068</v>
+        <v>0.07984566465369443</v>
       </c>
       <c r="AC4">
-        <v>-0.1076462243493068</v>
+        <v>-0.07984566465369443</v>
       </c>
       <c r="AD4">
-        <v>515</v>
+        <v>1127</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>515</v>
+        <v>1127</v>
       </c>
       <c r="AG4">
-        <v>187.2</v>
+        <v>407.9</v>
       </c>
       <c r="AH4">
-        <v>0.3729181752353367</v>
+        <v>0.4792277926606285</v>
       </c>
       <c r="AI4">
-        <v>0.3042296786389414</v>
+        <v>0.3943454984429126</v>
       </c>
       <c r="AJ4">
-        <v>0.1777440182301557</v>
+        <v>0.2498468700232758</v>
       </c>
       <c r="AK4">
-        <v>0.1371428571428571</v>
+        <v>0.1907144193005423</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Bank of Oman SAOG (MSM:NBOB)</t>
+          <t>Bank Dhofar SAOG (MSM:BKDB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0144</v>
+        <v>-0.0116</v>
       </c>
       <c r="E5">
-        <v>-0.0257</v>
+        <v>-0.0454</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>109.9</v>
+        <v>101.6</v>
       </c>
       <c r="L5">
-        <v>0.3801452784503632</v>
+        <v>0.3409395973154362</v>
       </c>
       <c r="M5">
-        <v>39.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="N5">
-        <v>0.032368808239333</v>
+        <v>0.0522807581111468</v>
       </c>
       <c r="O5">
-        <v>0.3603275705186533</v>
+        <v>0.640748031496063</v>
       </c>
       <c r="P5">
-        <v>39.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="Q5">
-        <v>0.032368808239333</v>
+        <v>0.0522807581111468</v>
       </c>
       <c r="R5">
-        <v>0.3603275705186533</v>
+        <v>0.640748031496063</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>546.8</v>
+        <v>373.7</v>
       </c>
       <c r="V5">
-        <v>0.4469511198299819</v>
+        <v>0.3001124317378734</v>
       </c>
       <c r="W5">
-        <v>0.07644685587089595</v>
+        <v>0.05519939150277083</v>
       </c>
       <c r="X5">
-        <v>0.1368228585110135</v>
+        <v>0.1067731081180952</v>
       </c>
       <c r="Y5">
-        <v>-0.06037600264011758</v>
+        <v>-0.05157371661532439</v>
       </c>
       <c r="Z5">
-        <v>0.1280109812256465</v>
+        <v>0.1050923966708986</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1076719029888328</v>
+        <v>0.08131656578326368</v>
       </c>
       <c r="AC5">
-        <v>-0.1076719029888328</v>
+        <v>-0.08131656578326368</v>
       </c>
       <c r="AD5">
-        <v>1186.3</v>
+        <v>1597.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1186.3</v>
+        <v>1597.1</v>
       </c>
       <c r="AG5">
-        <v>639.5</v>
+        <v>1223.4</v>
       </c>
       <c r="AH5">
-        <v>0.4923019463003694</v>
+        <v>0.5619040917566759</v>
       </c>
       <c r="AI5">
-        <v>0.4404633720714365</v>
+        <v>0.4581468732071142</v>
       </c>
       <c r="AJ5">
-        <v>0.3432819797090558</v>
+        <v>0.4955845418455804</v>
       </c>
       <c r="AK5">
-        <v>0.2979268576752854</v>
+        <v>0.3930854994698454</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank Dhofar SAOG (MSM:BKDB)</t>
+          <t>Oman Arab Bank SAOG (MSM:OAB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.019</v>
+        <v>0.0455</v>
       </c>
       <c r="E6">
-        <v>-0.128</v>
+        <v>-0.0406</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>59.5</v>
+        <v>60.8</v>
       </c>
       <c r="L6">
-        <v>0.2276205049732211</v>
+        <v>0.2341162880246438</v>
       </c>
       <c r="M6">
-        <v>39.9</v>
+        <v>27.4</v>
       </c>
       <c r="N6">
-        <v>0.02922648696161734</v>
+        <v>0.04860741529182189</v>
       </c>
       <c r="O6">
-        <v>0.6705882352941176</v>
+        <v>0.4506578947368421</v>
       </c>
       <c r="P6">
-        <v>39.9</v>
+        <v>27.4</v>
       </c>
       <c r="Q6">
-        <v>0.02922648696161734</v>
+        <v>0.04860741529182189</v>
       </c>
       <c r="R6">
-        <v>0.6705882352941176</v>
+        <v>0.4506578947368421</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>452.9</v>
+        <v>486.1</v>
       </c>
       <c r="V6">
-        <v>0.3317462642836214</v>
+        <v>0.8623381231151321</v>
       </c>
       <c r="W6">
-        <v>0.0323651000870322</v>
+        <v>0.04728941432682585</v>
       </c>
       <c r="X6">
-        <v>0.1409747329215973</v>
+        <v>0.09040949088511395</v>
       </c>
       <c r="Y6">
-        <v>-0.1086096328345651</v>
+        <v>-0.0431200765582881</v>
       </c>
       <c r="Z6">
-        <v>0.09790262172284643</v>
+        <v>0.2668242063084352</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1083605968200139</v>
+        <v>0.08153214253567471</v>
       </c>
       <c r="AC6">
-        <v>-0.1083605968200139</v>
+        <v>-0.08153214253567471</v>
       </c>
       <c r="AD6">
-        <v>1447.9</v>
+        <v>389.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1447.9</v>
+        <v>389.3</v>
       </c>
       <c r="AG6">
-        <v>995.0000000000001</v>
+        <v>-96.80000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.5146990864171199</v>
+        <v>0.4084994753410283</v>
       </c>
       <c r="AI6">
-        <v>0.4402919264102175</v>
+        <v>0.226997084548105</v>
       </c>
       <c r="AJ6">
-        <v>0.4215744428438268</v>
+        <v>-0.2073249089740844</v>
       </c>
       <c r="AK6">
-        <v>0.3508957539850473</v>
+        <v>-0.07876963137765482</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bank muscat SAOG (MSM:BKMB)</t>
+          <t>Bank Muscat SAOG (MSM:BKMB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0281</v>
+        <v>0.0254</v>
       </c>
       <c r="E7">
-        <v>0.0308</v>
+        <v>0.0311</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,28 +1216,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>513.6</v>
+        <v>548.9</v>
       </c>
       <c r="L7">
-        <v>0.4545937334041424</v>
+        <v>0.4559727529489949</v>
       </c>
       <c r="M7">
-        <v>297.1</v>
+        <v>311</v>
       </c>
       <c r="N7">
-        <v>0.05528161807119067</v>
+        <v>0.05974220565918129</v>
       </c>
       <c r="O7">
-        <v>0.5784657320872274</v>
+        <v>0.5665877208963381</v>
       </c>
       <c r="P7">
-        <v>297.1</v>
+        <v>311</v>
       </c>
       <c r="Q7">
-        <v>0.05528161807119067</v>
+        <v>0.05974220565918129</v>
       </c>
       <c r="R7">
-        <v>0.5784657320872274</v>
+        <v>0.5665877208963381</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1246,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1518.3</v>
+        <v>2098.4</v>
       </c>
       <c r="V7">
-        <v>0.2825112107623318</v>
+        <v>0.4030966056438136</v>
       </c>
       <c r="W7">
-        <v>0.09385964912280702</v>
+        <v>0.09728992006239033</v>
       </c>
       <c r="X7">
-        <v>0.1230430694454147</v>
+        <v>0.0888290664742641</v>
       </c>
       <c r="Y7">
-        <v>-0.02918342032260765</v>
+        <v>0.008460853588126233</v>
       </c>
       <c r="Z7">
-        <v>0.3715714003815036</v>
+        <v>0.1560640435599922</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1126092921475042</v>
+        <v>0.08190353762367748</v>
       </c>
       <c r="AC7">
-        <v>-0.1126092921475042</v>
+        <v>-0.08190353762367748</v>
       </c>
       <c r="AD7">
-        <v>3589.9</v>
+        <v>3297.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3589.9</v>
+        <v>3297.5</v>
       </c>
       <c r="AG7">
-        <v>2071.6</v>
+        <v>1199.1</v>
       </c>
       <c r="AH7">
-        <v>0.4004707614734165</v>
+        <v>0.3877951829899332</v>
       </c>
       <c r="AI7">
-        <v>0.388862410364176</v>
+        <v>0.3550853389328595</v>
       </c>
       <c r="AJ7">
-        <v>0.2782202285821728</v>
+        <v>0.1872189607794154</v>
       </c>
       <c r="AK7">
-        <v>0.2685680948985545</v>
+        <v>0.1668173787231674</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0771</v>
+        <v>0.0833</v>
       </c>
       <c r="E8">
-        <v>0.0535</v>
+        <v>0.132</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,85 +1338,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>84.7</v>
+        <v>136.3</v>
       </c>
       <c r="L8">
-        <v>0.3514522821576764</v>
+        <v>0.4904641957538684</v>
       </c>
       <c r="M8">
-        <v>330.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="N8">
-        <v>0.2608352411778637</v>
+        <v>0.05096207473508086</v>
       </c>
       <c r="O8">
-        <v>3.900826446280991</v>
+        <v>0.5363169479090242</v>
       </c>
       <c r="P8">
-        <v>70.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Q8">
-        <v>0.05581432067577169</v>
+        <v>0.05096207473508086</v>
       </c>
       <c r="R8">
-        <v>0.8347107438016529</v>
+        <v>0.5363169479090242</v>
       </c>
       <c r="S8">
-        <v>259.7</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.7860169491525424</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>216.2</v>
+        <v>1128.9</v>
       </c>
       <c r="V8">
-        <v>0.1706797189547643</v>
+        <v>0.7870189626324596</v>
       </c>
       <c r="W8">
-        <v>0.05495717622631716</v>
+        <v>0.07971226387508042</v>
       </c>
       <c r="X8">
-        <v>0.1656115631938485</v>
+        <v>0.1110556317156045</v>
       </c>
       <c r="Y8">
-        <v>-0.1106543869675314</v>
+        <v>-0.03134336784052404</v>
       </c>
       <c r="Z8">
-        <v>0.05809048617639261</v>
+        <v>0.09958431878449077</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1174718848592197</v>
+        <v>0.08606338042770291</v>
       </c>
       <c r="AC8">
-        <v>-0.1174718848592197</v>
+        <v>-0.08606338042770291</v>
       </c>
       <c r="AD8">
-        <v>2026.7</v>
+        <v>2062</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2026.7</v>
+        <v>2062</v>
       </c>
       <c r="AG8">
-        <v>1810.5</v>
+        <v>933.0999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.6153822797109371</v>
+        <v>0.5897494565839149</v>
       </c>
       <c r="AI8">
-        <v>0.5423914788845474</v>
+        <v>0.501422561583542</v>
       </c>
       <c r="AJ8">
-        <v>0.5883595476407124</v>
+        <v>0.3941288278775079</v>
       </c>
       <c r="AK8">
-        <v>0.5142881490739688</v>
+        <v>0.3127639605818864</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03545</v>
+        <v>0.0263</v>
       </c>
       <c r="E2">
-        <v>0.0322</v>
+        <v>0.0379</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1090</v>
+        <v>584.1</v>
       </c>
       <c r="L2">
-        <v>0.4200061652281135</v>
+        <v>0.4748780487804878</v>
       </c>
       <c r="M2">
-        <v>615.6</v>
+        <v>363.2</v>
       </c>
       <c r="N2">
-        <v>0.05780173142288408</v>
+        <v>0.07392180408279567</v>
       </c>
       <c r="O2">
-        <v>0.5647706422018349</v>
+        <v>0.6218113336757404</v>
       </c>
       <c r="P2">
-        <v>615.6</v>
+        <v>363.2</v>
       </c>
       <c r="Q2">
-        <v>0.05780173142288408</v>
+        <v>0.07392180408279567</v>
       </c>
       <c r="R2">
-        <v>0.5647706422018349</v>
+        <v>0.6218113336757404</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5033</v>
+        <v>3777.2</v>
       </c>
       <c r="V2">
-        <v>0.4725732850087322</v>
+        <v>0.768770480125374</v>
       </c>
       <c r="W2">
-        <v>0.08099214823911943</v>
+        <v>0.09752880280514277</v>
       </c>
       <c r="X2">
-        <v>0.09358289668954142</v>
+        <v>0.08224084094472536</v>
       </c>
       <c r="Y2">
-        <v>-0.01259074845042199</v>
+        <v>0.01528796186041741</v>
       </c>
       <c r="Z2">
-        <v>0.1455973519593817</v>
+        <v>0.1711161503039746</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08142435415946919</v>
+        <v>0.08022164117997038</v>
       </c>
       <c r="AC2">
-        <v>-0.08142435415946919</v>
+        <v>-0.08022164117997038</v>
       </c>
       <c r="AD2">
-        <v>8917.1</v>
+        <v>1192.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8917.1</v>
+        <v>1192.9</v>
       </c>
       <c r="AG2">
-        <v>3884.1</v>
+        <v>-2584.3</v>
       </c>
       <c r="AH2">
-        <v>0.4557143806248179</v>
+        <v>0.1953588156300154</v>
       </c>
       <c r="AI2">
-        <v>0.3836384365521544</v>
+        <v>0.1599404698058565</v>
       </c>
       <c r="AJ2">
-        <v>0.2672368122303792</v>
+        <v>-1.109617861743237</v>
       </c>
       <c r="AK2">
-        <v>0.2132890365448505</v>
+        <v>-0.7020265130935563</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ahli Bank SAOG (MSM:ABOB)</t>
+          <t>Bank Muscat SAOG (MSM:BKMB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07980000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="E3">
-        <v>0.0549</v>
+        <v>0.0379</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>96.90000000000001</v>
+        <v>584.1</v>
       </c>
       <c r="L3">
-        <v>0.4438845625286303</v>
+        <v>0.4748780487804878</v>
       </c>
       <c r="M3">
-        <v>79.2</v>
+        <v>363.2</v>
       </c>
       <c r="N3">
-        <v>0.08110599078341015</v>
+        <v>0.07392180408279567</v>
       </c>
       <c r="O3">
-        <v>0.8173374613003096</v>
+        <v>0.6218113336757404</v>
       </c>
       <c r="P3">
-        <v>79.2</v>
+        <v>363.2</v>
       </c>
       <c r="Q3">
-        <v>0.08110599078341015</v>
+        <v>0.07392180408279567</v>
       </c>
       <c r="R3">
-        <v>0.8173374613003096</v>
+        <v>0.6218113336757404</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,670 +758,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>226.8</v>
+        <v>3777.2</v>
       </c>
       <c r="V3">
-        <v>0.232258064516129</v>
+        <v>0.768770480125374</v>
       </c>
       <c r="W3">
-        <v>0.08227203260315843</v>
+        <v>0.09752880280514277</v>
       </c>
       <c r="X3">
-        <v>0.08389362585645024</v>
+        <v>0.08224084094472536</v>
       </c>
       <c r="Y3">
-        <v>-0.001621593253291809</v>
+        <v>0.01528796186041741</v>
       </c>
       <c r="Z3">
-        <v>0.1599267399267399</v>
+        <v>0.1711161503039746</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07913623110316884</v>
+        <v>0.08022164117997038</v>
       </c>
       <c r="AC3">
-        <v>-0.07913623110316884</v>
+        <v>-0.08022164117997038</v>
       </c>
       <c r="AD3">
-        <v>444.2</v>
+        <v>1192.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>444.2</v>
+        <v>1192.9</v>
       </c>
       <c r="AG3">
-        <v>217.4</v>
+        <v>-2584.3</v>
       </c>
       <c r="AH3">
-        <v>0.3126627718730203</v>
+        <v>0.1953588156300154</v>
       </c>
       <c r="AI3">
-        <v>0.2487400604770971</v>
+        <v>0.1599404698058565</v>
       </c>
       <c r="AJ3">
-        <v>0.182092302537901</v>
+        <v>-1.109617861743237</v>
       </c>
       <c r="AK3">
-        <v>0.1394483643361129</v>
+        <v>-0.7020265130935563</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>National Bank of Oman SAOG (MSM:NBOB)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0175</v>
-      </c>
-      <c r="E4">
-        <v>0.0333</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>145.5</v>
-      </c>
-      <c r="L4">
-        <v>0.4311111111111111</v>
-      </c>
-      <c r="M4">
-        <v>59.8</v>
-      </c>
-      <c r="N4">
-        <v>0.0488282844778313</v>
-      </c>
-      <c r="O4">
-        <v>0.4109965635738831</v>
-      </c>
-      <c r="P4">
-        <v>59.8</v>
-      </c>
-      <c r="Q4">
-        <v>0.0488282844778313</v>
-      </c>
-      <c r="R4">
-        <v>0.4109965635738831</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>719.1</v>
-      </c>
-      <c r="V4">
-        <v>0.5871642034784029</v>
-      </c>
-      <c r="W4">
-        <v>0.09654943596549435</v>
-      </c>
-      <c r="X4">
-        <v>0.09675630249396888</v>
-      </c>
-      <c r="Y4">
-        <v>-0.000206866528474528</v>
-      </c>
-      <c r="Z4">
-        <v>0.1572327044025157</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07984566465369443</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07984566465369443</v>
-      </c>
-      <c r="AD4">
-        <v>1127</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>1127</v>
-      </c>
-      <c r="AG4">
-        <v>407.9</v>
-      </c>
-      <c r="AH4">
-        <v>0.4792277926606285</v>
-      </c>
-      <c r="AI4">
-        <v>0.3943454984429126</v>
-      </c>
-      <c r="AJ4">
-        <v>0.2498468700232758</v>
-      </c>
-      <c r="AK4">
-        <v>0.1907144193005423</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bank Dhofar SAOG (MSM:BKDB)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.0116</v>
-      </c>
-      <c r="E5">
-        <v>-0.0454</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>101.6</v>
-      </c>
-      <c r="L5">
-        <v>0.3409395973154362</v>
-      </c>
-      <c r="M5">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="N5">
-        <v>0.0522807581111468</v>
-      </c>
-      <c r="O5">
-        <v>0.640748031496063</v>
-      </c>
-      <c r="P5">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="Q5">
-        <v>0.0522807581111468</v>
-      </c>
-      <c r="R5">
-        <v>0.640748031496063</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>373.7</v>
-      </c>
-      <c r="V5">
-        <v>0.3001124317378734</v>
-      </c>
-      <c r="W5">
-        <v>0.05519939150277083</v>
-      </c>
-      <c r="X5">
-        <v>0.1067731081180952</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05157371661532439</v>
-      </c>
-      <c r="Z5">
-        <v>0.1050923966708986</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.08131656578326368</v>
-      </c>
-      <c r="AC5">
-        <v>-0.08131656578326368</v>
-      </c>
-      <c r="AD5">
-        <v>1597.1</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1597.1</v>
-      </c>
-      <c r="AG5">
-        <v>1223.4</v>
-      </c>
-      <c r="AH5">
-        <v>0.5619040917566759</v>
-      </c>
-      <c r="AI5">
-        <v>0.4581468732071142</v>
-      </c>
-      <c r="AJ5">
-        <v>0.4955845418455804</v>
-      </c>
-      <c r="AK5">
-        <v>0.3930854994698454</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Oman Arab Bank SAOG (MSM:OAB)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0455</v>
-      </c>
-      <c r="E6">
-        <v>-0.0406</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>60.8</v>
-      </c>
-      <c r="L6">
-        <v>0.2341162880246438</v>
-      </c>
-      <c r="M6">
-        <v>27.4</v>
-      </c>
-      <c r="N6">
-        <v>0.04860741529182189</v>
-      </c>
-      <c r="O6">
-        <v>0.4506578947368421</v>
-      </c>
-      <c r="P6">
-        <v>27.4</v>
-      </c>
-      <c r="Q6">
-        <v>0.04860741529182189</v>
-      </c>
-      <c r="R6">
-        <v>0.4506578947368421</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>486.1</v>
-      </c>
-      <c r="V6">
-        <v>0.8623381231151321</v>
-      </c>
-      <c r="W6">
-        <v>0.04728941432682585</v>
-      </c>
-      <c r="X6">
-        <v>0.09040949088511395</v>
-      </c>
-      <c r="Y6">
-        <v>-0.0431200765582881</v>
-      </c>
-      <c r="Z6">
-        <v>0.2668242063084352</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.08153214253567471</v>
-      </c>
-      <c r="AC6">
-        <v>-0.08153214253567471</v>
-      </c>
-      <c r="AD6">
-        <v>389.3</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>389.3</v>
-      </c>
-      <c r="AG6">
-        <v>-96.80000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.4084994753410283</v>
-      </c>
-      <c r="AI6">
-        <v>0.226997084548105</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.2073249089740844</v>
-      </c>
-      <c r="AK6">
-        <v>-0.07876963137765482</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bank Muscat SAOG (MSM:BKMB)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0254</v>
-      </c>
-      <c r="E7">
-        <v>0.0311</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>548.9</v>
-      </c>
-      <c r="L7">
-        <v>0.4559727529489949</v>
-      </c>
-      <c r="M7">
-        <v>311</v>
-      </c>
-      <c r="N7">
-        <v>0.05974220565918129</v>
-      </c>
-      <c r="O7">
-        <v>0.5665877208963381</v>
-      </c>
-      <c r="P7">
-        <v>311</v>
-      </c>
-      <c r="Q7">
-        <v>0.05974220565918129</v>
-      </c>
-      <c r="R7">
-        <v>0.5665877208963381</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>2098.4</v>
-      </c>
-      <c r="V7">
-        <v>0.4030966056438136</v>
-      </c>
-      <c r="W7">
-        <v>0.09728992006239033</v>
-      </c>
-      <c r="X7">
-        <v>0.0888290664742641</v>
-      </c>
-      <c r="Y7">
-        <v>0.008460853588126233</v>
-      </c>
-      <c r="Z7">
-        <v>0.1560640435599922</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.08190353762367748</v>
-      </c>
-      <c r="AC7">
-        <v>-0.08190353762367748</v>
-      </c>
-      <c r="AD7">
-        <v>3297.5</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>3297.5</v>
-      </c>
-      <c r="AG7">
-        <v>1199.1</v>
-      </c>
-      <c r="AH7">
-        <v>0.3877951829899332</v>
-      </c>
-      <c r="AI7">
-        <v>0.3550853389328595</v>
-      </c>
-      <c r="AJ7">
-        <v>0.1872189607794154</v>
-      </c>
-      <c r="AK7">
-        <v>0.1668173787231674</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Oman</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sohar International Bank SAOG (MSM:BKSB)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0833</v>
-      </c>
-      <c r="E8">
-        <v>0.132</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>136.3</v>
-      </c>
-      <c r="L8">
-        <v>0.4904641957538684</v>
-      </c>
-      <c r="M8">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="N8">
-        <v>0.05096207473508086</v>
-      </c>
-      <c r="O8">
-        <v>0.5363169479090242</v>
-      </c>
-      <c r="P8">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="Q8">
-        <v>0.05096207473508086</v>
-      </c>
-      <c r="R8">
-        <v>0.5363169479090242</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1128.9</v>
-      </c>
-      <c r="V8">
-        <v>0.7870189626324596</v>
-      </c>
-      <c r="W8">
-        <v>0.07971226387508042</v>
-      </c>
-      <c r="X8">
-        <v>0.1110556317156045</v>
-      </c>
-      <c r="Y8">
-        <v>-0.03134336784052404</v>
-      </c>
-      <c r="Z8">
-        <v>0.09958431878449077</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.08606338042770291</v>
-      </c>
-      <c r="AC8">
-        <v>-0.08606338042770291</v>
-      </c>
-      <c r="AD8">
-        <v>2062</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>2062</v>
-      </c>
-      <c r="AG8">
-        <v>933.0999999999999</v>
-      </c>
-      <c r="AH8">
-        <v>0.5897494565839149</v>
-      </c>
-      <c r="AI8">
-        <v>0.501422561583542</v>
-      </c>
-      <c r="AJ8">
-        <v>0.3941288278775079</v>
-      </c>
-      <c r="AK8">
-        <v>0.3127639605818864</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0263</v>
+        <v>0.0331</v>
       </c>
       <c r="E2">
         <v>0.0379</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>584.1</v>
+        <v>1113.7</v>
       </c>
       <c r="L2">
-        <v>0.4748780487804878</v>
+        <v>0.4701933631681162</v>
       </c>
       <c r="M2">
-        <v>363.2</v>
+        <v>1064.1</v>
       </c>
       <c r="N2">
-        <v>0.07392180408279567</v>
+        <v>0.105122252408002</v>
       </c>
       <c r="O2">
-        <v>0.6218113336757404</v>
+        <v>0.9554637694172576</v>
       </c>
       <c r="P2">
-        <v>363.2</v>
+        <v>588.9</v>
       </c>
       <c r="Q2">
-        <v>0.07392180408279567</v>
+        <v>0.05817732773524327</v>
       </c>
       <c r="R2">
-        <v>0.6218113336757404</v>
+        <v>0.5287779473825985</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>475.2</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.446574570059205</v>
       </c>
       <c r="U2">
-        <v>3777.2</v>
+        <v>8055.1</v>
       </c>
       <c r="V2">
-        <v>0.768770480125374</v>
+        <v>0.7957619165225982</v>
       </c>
       <c r="W2">
-        <v>0.09752880280514277</v>
+        <v>0.07371794871794873</v>
       </c>
       <c r="X2">
-        <v>0.08224084094472536</v>
+        <v>0.08659244079116926</v>
       </c>
       <c r="Y2">
-        <v>0.01528796186041741</v>
+        <v>-0.01287449207322053</v>
       </c>
       <c r="Z2">
-        <v>0.1711161503039746</v>
+        <v>0.1473770665206543</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08022164117997038</v>
+        <v>0.08180662287011151</v>
       </c>
       <c r="AC2">
-        <v>-0.08022164117997038</v>
+        <v>-0.08180662287011151</v>
       </c>
       <c r="AD2">
-        <v>1192.9</v>
+        <v>4712.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1192.9</v>
+        <v>4712.2</v>
       </c>
       <c r="AG2">
-        <v>-2584.3</v>
+        <v>-3342.900000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1953588156300154</v>
+        <v>0.3176471381288465</v>
       </c>
       <c r="AI2">
-        <v>0.1599404698058565</v>
+        <v>0.2668622365187056</v>
       </c>
       <c r="AJ2">
-        <v>-1.109617861743237</v>
+        <v>-0.4930821877396898</v>
       </c>
       <c r="AK2">
-        <v>-0.7020265130935563</v>
+        <v>-0.348120841013465</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +701,605 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Oman Arab Bank SAOG (MSM:OAB)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0331</v>
+      </c>
+      <c r="E3">
+        <v>-0.0443</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>60.4</v>
+      </c>
+      <c r="L3">
+        <v>0.2341085271317829</v>
+      </c>
+      <c r="M3">
+        <v>138.6</v>
+      </c>
+      <c r="N3">
+        <v>0.2075471698113208</v>
+      </c>
+      <c r="O3">
+        <v>2.294701986754967</v>
+      </c>
+      <c r="P3">
+        <v>27.8</v>
+      </c>
+      <c r="Q3">
+        <v>0.0416292303084756</v>
+      </c>
+      <c r="R3">
+        <v>0.4602649006622517</v>
+      </c>
+      <c r="S3">
+        <v>110.8</v>
+      </c>
+      <c r="T3">
+        <v>0.7994227994227995</v>
+      </c>
+      <c r="U3">
+        <v>700.6</v>
+      </c>
+      <c r="V3">
+        <v>1.049116501946691</v>
+      </c>
+      <c r="W3">
+        <v>0.04556083578486837</v>
+      </c>
+      <c r="X3">
+        <v>0.08006964316513843</v>
+      </c>
+      <c r="Y3">
+        <v>-0.03450880738027006</v>
+      </c>
+      <c r="Z3">
+        <v>0.2099438522255676</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.07872052166230691</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07872052166230691</v>
+      </c>
+      <c r="AD3">
+        <v>105.8</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>105.8</v>
+      </c>
+      <c r="AG3">
+        <v>-594.8000000000001</v>
+      </c>
+      <c r="AH3">
+        <v>0.1367631851085833</v>
+      </c>
+      <c r="AI3">
+        <v>0.07080238238640166</v>
+      </c>
+      <c r="AJ3">
+        <v>-8.147945205479466</v>
+      </c>
+      <c r="AK3">
+        <v>-0.7494015371046997</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Bank Muscat SAOG (MSM:BKMB)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.0263</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0.0379</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>584.1</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>0.4748780487804878</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>363.2</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.07392180408279567</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>0.6218113336757404</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>363.2</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>0.07392180408279567</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>0.6218113336757404</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>3777.2</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>0.768770480125374</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>0.09752880280514277</v>
       </c>
-      <c r="X3">
-        <v>0.08224084094472536</v>
-      </c>
-      <c r="Y3">
-        <v>0.01528796186041741</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.08223531905345349</v>
+      </c>
+      <c r="Y4">
+        <v>0.01529348375168928</v>
+      </c>
+      <c r="Z4">
         <v>0.1711161503039746</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.08022164117997038</v>
-      </c>
-      <c r="AC3">
-        <v>-0.08022164117997038</v>
-      </c>
-      <c r="AD3">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.08021719803883742</v>
+      </c>
+      <c r="AC4">
+        <v>-0.08021719803883742</v>
+      </c>
+      <c r="AD4">
         <v>1192.9</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>1192.9</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>-2584.3</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.1953588156300154</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.1599404698058565</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>-1.109617861743237</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>-0.7020265130935563</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ahli Bank SAOG (MSM:ABOB)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.08</v>
+      </c>
+      <c r="E5">
+        <v>0.0489</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="L5">
+        <v>0.4212095400340716</v>
+      </c>
+      <c r="M5">
+        <v>11.3</v>
+      </c>
+      <c r="N5">
+        <v>0.0112214498510427</v>
+      </c>
+      <c r="O5">
+        <v>0.1142568250758342</v>
+      </c>
+      <c r="P5">
+        <v>11.3</v>
+      </c>
+      <c r="Q5">
+        <v>0.0112214498510427</v>
+      </c>
+      <c r="R5">
+        <v>0.1142568250758342</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>443</v>
+      </c>
+      <c r="V5">
+        <v>0.4399205561072492</v>
+      </c>
+      <c r="W5">
+        <v>0.07371794871794873</v>
+      </c>
+      <c r="X5">
+        <v>0.08659244079116926</v>
+      </c>
+      <c r="Y5">
+        <v>-0.01287449207322053</v>
+      </c>
+      <c r="Z5">
+        <v>0.1506093649775497</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.08180662287011151</v>
+      </c>
+      <c r="AC5">
+        <v>-0.08180662287011151</v>
+      </c>
+      <c r="AD5">
+        <v>415.4</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>415.4</v>
+      </c>
+      <c r="AG5">
+        <v>-27.60000000000002</v>
+      </c>
+      <c r="AH5">
+        <v>0.2920416197975253</v>
+      </c>
+      <c r="AI5">
+        <v>0.2236459567136858</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.02818051868490915</v>
+      </c>
+      <c r="AK5">
+        <v>-0.0195135746606335</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bank Dhofar SAOG (MSM:BKDB)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.00971</v>
+      </c>
+      <c r="E6">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>107.7</v>
+      </c>
+      <c r="L6">
+        <v>0.3402843601895735</v>
+      </c>
+      <c r="M6">
+        <v>202.7</v>
+      </c>
+      <c r="N6">
+        <v>0.1669549460505725</v>
+      </c>
+      <c r="O6">
+        <v>1.882079851439183</v>
+      </c>
+      <c r="P6">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q6">
+        <v>0.08121242072316942</v>
+      </c>
+      <c r="R6">
+        <v>0.915506035283194</v>
+      </c>
+      <c r="S6">
+        <v>104.1</v>
+      </c>
+      <c r="T6">
+        <v>0.5135668475579674</v>
+      </c>
+      <c r="U6">
+        <v>336</v>
+      </c>
+      <c r="V6">
+        <v>0.2767482085495429</v>
+      </c>
+      <c r="W6">
+        <v>0.05701731166287257</v>
+      </c>
+      <c r="X6">
+        <v>0.09662927054124859</v>
+      </c>
+      <c r="Y6">
+        <v>-0.03961195887837602</v>
+      </c>
+      <c r="Z6">
+        <v>0.1016932814959997</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.08485685252187707</v>
+      </c>
+      <c r="AC6">
+        <v>-0.08485685252187707</v>
+      </c>
+      <c r="AD6">
+        <v>975.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>975.5</v>
+      </c>
+      <c r="AG6">
+        <v>639.5</v>
+      </c>
+      <c r="AH6">
+        <v>0.4455151625867739</v>
+      </c>
+      <c r="AI6">
+        <v>0.3378940076203671</v>
+      </c>
+      <c r="AJ6">
+        <v>0.3450043159257661</v>
+      </c>
+      <c r="AK6">
+        <v>0.2506860054880439</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sohar International Bank SAOG (MSM:BKSB)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0958</v>
+      </c>
+      <c r="E7">
+        <v>0.254</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>262.6</v>
+      </c>
+      <c r="L7">
+        <v>0.7974491345277862</v>
+      </c>
+      <c r="M7">
+        <v>348.3</v>
+      </c>
+      <c r="N7">
+        <v>0.1501098995819506</v>
+      </c>
+      <c r="O7">
+        <v>1.326351865955826</v>
+      </c>
+      <c r="P7">
+        <v>88</v>
+      </c>
+      <c r="Q7">
+        <v>0.03792613024177908</v>
+      </c>
+      <c r="R7">
+        <v>0.3351104341203351</v>
+      </c>
+      <c r="S7">
+        <v>260.3</v>
+      </c>
+      <c r="T7">
+        <v>0.7473442434682744</v>
+      </c>
+      <c r="U7">
+        <v>2798.3</v>
+      </c>
+      <c r="V7">
+        <v>1.2060078438133</v>
+      </c>
+      <c r="W7">
+        <v>0.1280788177339902</v>
+      </c>
+      <c r="X7">
+        <v>0.09838066355060934</v>
+      </c>
+      <c r="Y7">
+        <v>0.02969815418338081</v>
+      </c>
+      <c r="Z7">
+        <v>0.1103774217335926</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.08525852879304291</v>
+      </c>
+      <c r="AC7">
+        <v>-0.08525852879304291</v>
+      </c>
+      <c r="AD7">
+        <v>2022.6</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>2022.6</v>
+      </c>
+      <c r="AG7">
+        <v>-775.7000000000003</v>
+      </c>
+      <c r="AH7">
+        <v>0.465725667180916</v>
+      </c>
+      <c r="AI7">
+        <v>0.5106673062842427</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.5022012171435972</v>
+      </c>
+      <c r="AK7">
+        <v>-0.6673262216104615</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
         <v>0</v>
       </c>
     </row>
